--- a/data/trans_camb/IP1010-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1010-Clase-trans_camb.xlsx
@@ -641,22 +641,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 0,0</t>
+          <t>-3,77; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 0,0</t>
+          <t>-3,82; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
+          <t>-1,88; 0,0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>-1,68; 0,0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-1,88; 0,0</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,91</t>
+          <t>0,0; 2,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -797,22 +797,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 0,0</t>
+          <t>-4,08; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 2,13</t>
+          <t>-2,27; 1,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 0,47</t>
+          <t>-1,48; 0,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,36</t>
+          <t>-0,75; 1,13</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,55</t>
+          <t>0,0; 5,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,61</t>
+          <t>0,0; 2,66</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 0,0</t>
+          <t>-1,62; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 0,0</t>
+          <t>-1,6; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 1,2</t>
+          <t>-0,76; 1,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,41</t>
+          <t>-0,73; 1,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 0,61</t>
+          <t>-0,7; 0,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,66</t>
+          <t>-0,67; 0,67</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,3</t>
+          <t>0,0; 2,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,58</t>
+          <t>0,0; 1,94</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 1,0</t>
+          <t>-1,66; 0,99</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,84</t>
+          <t>-1,19; 1,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 1,4</t>
+          <t>-0,6; 1,41</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 1,35</t>
+          <t>-0,64; 1,34</t>
         </is>
       </c>
     </row>
@@ -1411,27 +1411,27 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 5,54</t>
+          <t>-1,62; 5,74</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 0,0</t>
+          <t>-4,04; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 1,8</t>
+          <t>-4,33; 1,78</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 0,0</t>
+          <t>-6,05; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 2,3</t>
+          <t>-2,11; 2,06</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,67</t>
+          <t>-0,28; 0,68</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 0,09</t>
+          <t>-0,51; 0,13</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 0,34</t>
+          <t>-0,89; 0,33</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 0,69</t>
+          <t>-0,59; 0,7</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 0,31</t>
+          <t>-0,43; 0,32</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 0,31</t>
+          <t>-0,41; 0,35</t>
         </is>
       </c>
     </row>
@@ -1653,22 +1653,22 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-88,27; 166,32</t>
+          <t>-89,05; 150,09</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-73,99; 305,77</t>
+          <t>-71,9; 263,87</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-75,6; 160,13</t>
+          <t>-75,6; 167,59</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-71,17; 153,18</t>
+          <t>-73,78; 209,87</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1010-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1010-Clase-trans_camb.xlsx
@@ -641,22 +641,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 0,0</t>
+          <t>-4,05; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 0,0</t>
+          <t>-4,63; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 0,0</t>
+          <t>-1,67; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 0,0</t>
+          <t>-1,5; 0,0</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,74</t>
+          <t>0,0; 2,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 0,0</t>
+          <t>-3,72; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 0,47</t>
+          <t>-1,36; 0,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,13</t>
+          <t>-0,75; 1,49</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,93</t>
+          <t>0,0; 5,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,66</t>
+          <t>0,0; 3,12</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 0,0</t>
+          <t>-1,93; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,41</t>
+          <t>-1,08; 1,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,39</t>
+          <t>-0,74; 1,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,61</t>
+          <t>-0,73; 0,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,67</t>
+          <t>-0,69; 0,67</t>
         </is>
       </c>
     </row>
@@ -1260,27 +1260,27 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,94</t>
+          <t>0,0; 1,95</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 0,99</t>
+          <t>-1,67; 1,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 1,88</t>
+          <t>-1,19; 1,91</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,41</t>
+          <t>-0,61; 1,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,34</t>
+          <t>-0,61; 1,33</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 5,74</t>
+          <t>-1,62; 5,56</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 0,0</t>
+          <t>-4,09; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 1,78</t>
+          <t>-4,4; 1,76</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 0,0</t>
+          <t>-6,94; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 2,06</t>
+          <t>-2,1; 2,13</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,38; -0,41</t>
+          <t>-3,47; -0,4</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 0,68</t>
+          <t>-0,3; 0,6</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,13</t>
+          <t>-0,58; 0,08</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 0,33</t>
+          <t>-0,89; 0,28</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 0,7</t>
+          <t>-0,6; 0,68</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 0,32</t>
+          <t>-0,42; 0,36</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,35</t>
+          <t>-0,41; 0,34</t>
         </is>
       </c>
     </row>
@@ -1653,22 +1653,22 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-89,05; 150,09</t>
+          <t>-87,57; 201,55</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-71,9; 263,87</t>
+          <t>-70,51; 261,15</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-75,6; 167,59</t>
+          <t>-72,7; 178,03</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-73,78; 209,87</t>
+          <t>-77,33; 153,68</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1010-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1010-Clase-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-0,69</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-0,69</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,69</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,69</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,79; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,05; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 0,0</t>
+          <t>-1,68; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 0,0</t>
+          <t>-1,88; 0,0</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,75</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,02</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,48</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,75</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,02</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,7</t>
+          <t>-3,76; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,29; 2,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 0,0</t>
+          <t>0,0; 2,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 1,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 0,47</t>
+          <t>-1,79; 0,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,49</t>
+          <t>-0,75; 1,36</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-2,85%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-2,85%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -910,17 +910,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>0,96</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,96</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,12</t>
+          <t>0,0; 2,61</t>
         </is>
       </c>
     </row>
@@ -986,17 +986,17 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,22</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,33</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-0,32</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-0,32</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,22</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,33</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 0,0</t>
+          <t>-0,89; 1,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 0,0</t>
+          <t>-0,74; 1,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,13</t>
+          <t>-1,86; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,7</t>
+          <t>-1,75; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,56</t>
+          <t>-0,68; 0,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,67</t>
+          <t>-0,7; 0,66</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>61,45%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>92,01%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>61,45%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>92,01%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,17 +1217,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,06</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,38</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0,6</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>0,38</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,06</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,45</t>
+          <t>-1,66; 1,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,95</t>
+          <t>-1,17; 1,84</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 1,0</t>
+          <t>0,0; 3,3</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 1,91</t>
+          <t>0,0; 1,58</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 1,33</t>
+          <t>-0,61; 1,4</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 1,33</t>
+          <t>-0,62; 1,35</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-10,67%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>69,48%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-10,67%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>69,48%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1373,22 +1373,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-0,85</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-1,73</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>0,59</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>-0,81</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-0,85</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-1,73</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 5,56</t>
+          <t>-4,3; 1,8</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 0,0</t>
+          <t>-5,27; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 1,76</t>
+          <t>-1,62; 5,54</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 0,0</t>
+          <t>-4,76; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 2,13</t>
+          <t>-2,11; 2,3</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,47; -0,4</t>
+          <t>-3,38; -0,41</t>
         </is>
       </c>
     </row>
@@ -1449,17 +1449,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-49,37%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>73,48%</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-49,37%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-0,21</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>0,03</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>0,12</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>-0,12</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-0,21</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>0,03</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 0,6</t>
+          <t>-0,88; 0,34</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 0,08</t>
+          <t>-0,61; 0,69</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 0,28</t>
+          <t>-0,26; 0,67</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 0,68</t>
+          <t>-0,59; 0,09</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,36</t>
+          <t>-0,43; 0,31</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,34</t>
+          <t>-0,4; 0,31</t>
         </is>
       </c>
     </row>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-36,31%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>4,71%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>59,2%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>-60,03%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-36,31%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>4,71%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-88,27; 166,32</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-73,99; 305,77</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-87,57; 201,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-70,51; 261,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-72,7; 178,03</t>
+          <t>-75,6; 160,13</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-77,33; 153,68</t>
+          <t>-71,17; 153,18</t>
         </is>
       </c>
     </row>
